--- a/xls/square_un_16_tri3_11.xlsx
+++ b/xls/square_un_16_tri3_11.xlsx
@@ -456,12 +456,82 @@
         <v>10</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>174</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>340</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>122</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>618</v>
+      </c>
+      <c r="I9">
+        <v>-0.00022185769614929912</v>
+      </c>
+      <c r="J9">
+        <v>-1.1379177175423112</v>
+      </c>
+      <c r="K9">
+        <v>-0.23121943000698225</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>174</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>340</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>165</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>864</v>
+      </c>
+      <c r="I10">
+        <v>-0.00021608302930878763</v>
+      </c>
+      <c r="J10">
+        <v>-1.3684810697451213</v>
+      </c>
+      <c r="K10">
+        <v>0.06431228730934054</v>
+      </c>
+    </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F11">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
       </c>
       <c r="H11">
-        <v>726</v>
+        <v>906</v>
       </c>
       <c r="I11">
-        <v>-1.227092476160979</v>
+        <v>-0.0002098454488974628</v>
       </c>
       <c r="J11">
-        <v>-1.527925751113222</v>
+        <v>-1.2393134896492386</v>
       </c>
       <c r="K11">
-        <v>-0.5875075134982766</v>
+        <v>0.40544956847128766</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -496,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F12">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
       </c>
       <c r="H12">
-        <v>864</v>
+        <v>1104</v>
       </c>
       <c r="I12">
-        <v>-1.8232501519108222</v>
+        <v>-0.00019485051037482014</v>
       </c>
       <c r="J12">
-        <v>-1.8496520672759162</v>
+        <v>-0.9608228078137868</v>
       </c>
       <c r="K12">
-        <v>-0.8186519760843578</v>
+        <v>1.113416460801956</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -531,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F13">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
       </c>
       <c r="H13">
-        <v>1014</v>
+        <v>1266</v>
       </c>
       <c r="I13">
-        <v>-2.187917663733251</v>
+        <v>-0.0001742663747055841</v>
       </c>
       <c r="J13">
-        <v>-1.9400402844952676</v>
+        <v>-0.7619262931761398</v>
       </c>
       <c r="K13">
-        <v>-0.7410832423636322</v>
+        <v>1.289779287203331</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -566,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="B14">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F14">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
       </c>
       <c r="H14">
-        <v>1176</v>
+        <v>1362</v>
       </c>
       <c r="I14">
-        <v>-2.1973335876130564</v>
+        <v>-0.0001517490805021651</v>
       </c>
       <c r="J14">
-        <v>-1.7141326386602374</v>
+        <v>-0.5924797404651561</v>
       </c>
       <c r="K14">
-        <v>-0.3437287151973523</v>
+        <v>1.6829897545644075</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -601,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="B15">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F15">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
       </c>
       <c r="H15">
-        <v>1350</v>
+        <v>1596</v>
       </c>
       <c r="I15">
-        <v>-1.8876998737299482</v>
+        <v>-8.833859552488454e-5</v>
       </c>
       <c r="J15">
-        <v>-1.5374059309717834</v>
+        <v>-0.2888994929523577</v>
       </c>
       <c r="K15">
-        <v>-0.0377477597324918</v>
+        <v>2.6832471835213263</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -636,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B16">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F16">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16">
-        <v>1536</v>
+        <v>1842</v>
       </c>
       <c r="I16">
-        <v>-1.5496145916788397</v>
+        <v>-3.089450482891045e-5</v>
       </c>
       <c r="J16">
-        <v>-1.3338667517177156</v>
+        <v>-0.10310706680938155</v>
       </c>
       <c r="K16">
-        <v>0.2691503640917769</v>
+        <v>3.320141849567322</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -671,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B17">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F17">
-        <v>324</v>
+        <v>380</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
       <c r="H17">
-        <v>1734</v>
+        <v>2070</v>
       </c>
       <c r="I17">
-        <v>-1.2794334469300126</v>
+        <v>-1.1460257139524061e-7</v>
       </c>
       <c r="J17">
-        <v>-1.1438387006921449</v>
+        <v>-0.00030133535526814196</v>
       </c>
       <c r="K17">
-        <v>0.8531579629597378</v>
+        <v>2.6221291835584606</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -706,7 +776,7 @@
         <v>11</v>
       </c>
       <c r="B18">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F18">
-        <v>361</v>
+        <v>435</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18">
-        <v>1944</v>
+        <v>2388</v>
       </c>
       <c r="I18">
-        <v>-0.565806259523164</v>
+        <v>-2.7754064928703816e-9</v>
       </c>
       <c r="J18">
-        <v>-0.49105389027203683</v>
+        <v>-5.85257471732112e-6</v>
       </c>
       <c r="K18">
-        <v>1.9460623046719034</v>
+        <v>1.830880355651578</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -741,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B19">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F19">
-        <v>400</v>
+        <v>485</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19">
-        <v>2166</v>
+        <v>2676</v>
       </c>
       <c r="I19">
-        <v>-0.2503284696122391</v>
+        <v>-1.6713905940354644e-9</v>
       </c>
       <c r="J19">
-        <v>-0.21665578470280805</v>
+        <v>-3.3017992480433187e-6</v>
       </c>
       <c r="K19">
-        <v>2.131188867463485</v>
+        <v>1.7061801780122623</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -776,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B20">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -788,22 +858,22 @@
         <v>12</v>
       </c>
       <c r="F20">
-        <v>441</v>
+        <v>564</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20">
-        <v>2400</v>
+        <v>3138</v>
       </c>
       <c r="I20">
-        <v>-4.581284353406394e-5</v>
+        <v>-5.726356347241152e-10</v>
       </c>
       <c r="J20">
-        <v>-7.260836895671409e-5</v>
+        <v>-1.1463369671928869e-6</v>
       </c>
       <c r="K20">
-        <v>2.468904165188886</v>
+        <v>1.4809237898185645</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -811,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="B21">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -823,22 +893,22 @@
         <v>12</v>
       </c>
       <c r="F21">
-        <v>484</v>
+        <v>598</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21">
-        <v>2646</v>
+        <v>3330</v>
       </c>
       <c r="I21">
-        <v>-2.685973441998869e-6</v>
+        <v>-4.688112214804224e-10</v>
       </c>
       <c r="J21">
-        <v>-8.903602585145462e-6</v>
+        <v>-9.493802338019109e-7</v>
       </c>
       <c r="K21">
-        <v>2.053468243515584</v>
+        <v>1.4405358669681665</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -846,7 +916,7 @@
         <v>11</v>
       </c>
       <c r="B22">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -858,22 +928,22 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>529</v>
+        <v>668</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22">
-        <v>2904</v>
+        <v>3738</v>
       </c>
       <c r="I22">
-        <v>-2.974477772212005e-6</v>
+        <v>-4.1403279255267884e-10</v>
       </c>
       <c r="J22">
-        <v>-5.660376283486523e-6</v>
+        <v>-8.536140509836607e-7</v>
       </c>
       <c r="K22">
-        <v>1.924686433871276</v>
+        <v>1.4186114329117743</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -881,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="B23">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -893,22 +963,22 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>576</v>
+        <v>741</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>3174</v>
+        <v>4164</v>
       </c>
       <c r="I23">
-        <v>-1.860363401874013e-6</v>
+        <v>-3.9018767439964436e-10</v>
       </c>
       <c r="J23">
-        <v>-3.195897917657221e-6</v>
+        <v>-7.846408376164452e-7</v>
       </c>
       <c r="K23">
-        <v>1.792769625838597</v>
+        <v>1.3998930027820335</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -916,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="B24">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -928,22 +998,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-1.4810560908645598e-6</v>
+        <v>-3.4539008298484053e-10</v>
       </c>
       <c r="J24">
-        <v>-2.255566145799104e-6</v>
+        <v>-6.948073510581673e-7</v>
       </c>
       <c r="K24">
-        <v>1.7065660546640093</v>
+        <v>1.372872533562359</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -951,7 +1021,7 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -963,22 +1033,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-1.2035367082264858e-6</v>
+        <v>-3.3792401865104484e-10</v>
       </c>
       <c r="J25">
-        <v>-1.7247215484856e-6</v>
+        <v>-6.803536954811046e-7</v>
       </c>
       <c r="K25">
-        <v>1.6380048528847702</v>
+        <v>1.3693060910337573</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -986,7 +1056,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -998,22 +1068,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-1.0899265769044484e-6</v>
+        <v>-3.204287557922145e-10</v>
       </c>
       <c r="J26">
-        <v>-1.3927060455925184e-6</v>
+        <v>-6.348386253590839e-7</v>
       </c>
       <c r="K26">
-        <v>1.5757815142299207</v>
+        <v>1.3527063114414675</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1021,7 +1091,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -1033,22 +1103,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-1.1875222820529739e-6</v>
+        <v>-3.107626747750734e-10</v>
       </c>
       <c r="J27">
-        <v>-1.3861513895778394e-6</v>
+        <v>-6.266860780739141e-7</v>
       </c>
       <c r="K27">
-        <v>1.5594590226125042</v>
+        <v>1.3513107406876987</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1056,7 +1126,7 @@
         <v>11</v>
       </c>
       <c r="B28">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -1068,22 +1138,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-1.058576248714512e-6</v>
+        <v>-2.9577731523261096e-10</v>
       </c>
       <c r="J28">
-        <v>-1.2373132879986739e-6</v>
+        <v>-5.961428464812131e-7</v>
       </c>
       <c r="K28">
-        <v>1.5348213629058665</v>
+        <v>1.3400928692800151</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1091,7 +1161,7 @@
         <v>11</v>
       </c>
       <c r="B29">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -1103,22 +1173,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-9.837555295972924e-7</v>
+        <v>-3.023970375640715e-10</v>
       </c>
       <c r="J29">
-        <v>-1.1570382749806444e-6</v>
+        <v>-6.121906822960393e-7</v>
       </c>
       <c r="K29">
-        <v>1.5203187122536066</v>
+        <v>1.3464615561077284</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1126,7 +1196,7 @@
         <v>11</v>
       </c>
       <c r="B30">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -1138,22 +1208,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-9.495284692905158e-7</v>
+        <v>-2.85677431504904e-10</v>
       </c>
       <c r="J30">
-        <v>-1.1093532620215405e-6</v>
+        <v>-5.757422727507396e-7</v>
       </c>
       <c r="K30">
-        <v>1.509845297530136</v>
+        <v>1.332693441618083</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1161,7 +1231,7 @@
         <v>11</v>
       </c>
       <c r="B31">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -1173,22 +1243,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-9.196639702746191e-7</v>
+        <v>-2.698672826806508e-10</v>
       </c>
       <c r="J31">
-        <v>-1.0657379908827968e-6</v>
+        <v>-5.476906711569192e-7</v>
       </c>
       <c r="K31">
-        <v>1.4994918116790485</v>
+        <v>1.3224092410116965</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1196,7 +1266,7 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -1208,22 +1278,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-8.926478205243575e-7</v>
+        <v>-2.7240534435783026e-10</v>
       </c>
       <c r="J32">
-        <v>-1.0257428552883011e-6</v>
+        <v>-5.508288535506155e-7</v>
       </c>
       <c r="K32">
-        <v>1.4896389658719233</v>
+        <v>1.3235198079416333</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_11.xlsx
+++ b/xls/square_un_16_tri3_11.xlsx
@@ -482,13 +482,13 @@
         <v>618</v>
       </c>
       <c r="I9">
-        <v>-0.00022185769614929912</v>
+        <v>0.42659082184804964</v>
       </c>
       <c r="J9">
-        <v>-1.1379177175423112</v>
+        <v>-0.6590846356682485</v>
       </c>
       <c r="K9">
-        <v>-0.23121943000698225</v>
+        <v>-0.00562376135888669</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -517,13 +517,13 @@
         <v>864</v>
       </c>
       <c r="I10">
-        <v>-0.00021608302930878763</v>
+        <v>-1.609399231744271</v>
       </c>
       <c r="J10">
-        <v>-1.3684810697451213</v>
+        <v>-1.7227953913973524</v>
       </c>
       <c r="K10">
-        <v>0.06431228730934054</v>
+        <v>-0.752136369740017</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -552,13 +552,13 @@
         <v>906</v>
       </c>
       <c r="I11">
-        <v>-0.0002098454488974628</v>
+        <v>-1.9955983799504236</v>
       </c>
       <c r="J11">
-        <v>-1.2393134896492386</v>
+        <v>-1.8720997009563136</v>
       </c>
       <c r="K11">
-        <v>0.40544956847128766</v>
+        <v>-0.8685717842842002</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1104</v>
       </c>
       <c r="I12">
-        <v>-0.00019485051037482014</v>
+        <v>-1.8432354747918922</v>
       </c>
       <c r="J12">
-        <v>-0.9608228078137868</v>
+        <v>-1.4929538222848826</v>
       </c>
       <c r="K12">
-        <v>1.113416460801956</v>
+        <v>-0.29389918602880016</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1266</v>
       </c>
       <c r="I13">
-        <v>-0.0001742663747055841</v>
+        <v>-1.8203193909522741</v>
       </c>
       <c r="J13">
-        <v>-0.7619262931761398</v>
+        <v>-1.4963767576002893</v>
       </c>
       <c r="K13">
-        <v>1.289779287203331</v>
+        <v>-0.15908643803261693</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1362</v>
       </c>
       <c r="I14">
-        <v>-0.0001517490805021651</v>
+        <v>-1.7400165013314834</v>
       </c>
       <c r="J14">
-        <v>-0.5924797404651561</v>
+        <v>-1.43971019589799</v>
       </c>
       <c r="K14">
-        <v>1.6829897545644075</v>
+        <v>-0.12059141988916282</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1596</v>
       </c>
       <c r="I15">
-        <v>-8.833859552488454e-5</v>
+        <v>-1.5619487157516025</v>
       </c>
       <c r="J15">
-        <v>-0.2888994929523577</v>
+        <v>-1.3554720566655358</v>
       </c>
       <c r="K15">
-        <v>2.6832471835213263</v>
+        <v>0.11200265786269396</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -727,13 +727,13 @@
         <v>1842</v>
       </c>
       <c r="I16">
-        <v>-3.089450482891045e-5</v>
+        <v>-1.4501756393511822</v>
       </c>
       <c r="J16">
-        <v>-0.10310706680938155</v>
+        <v>-1.2516504594384064</v>
       </c>
       <c r="K16">
-        <v>3.320141849567322</v>
+        <v>0.017543832547895086</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -762,13 +762,13 @@
         <v>2070</v>
       </c>
       <c r="I17">
-        <v>-1.1460257139524061e-7</v>
+        <v>-0.23996035861669143</v>
       </c>
       <c r="J17">
-        <v>-0.00030133535526814196</v>
+        <v>-0.22962048080313713</v>
       </c>
       <c r="K17">
-        <v>2.6221291835584606</v>
+        <v>1.899426495677675</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -797,13 +797,13 @@
         <v>2388</v>
       </c>
       <c r="I18">
-        <v>-2.7754064928703816e-9</v>
+        <v>-1.057573016194422e-6</v>
       </c>
       <c r="J18">
-        <v>-5.85257471732112e-6</v>
+        <v>-9.917082519980902e-6</v>
       </c>
       <c r="K18">
-        <v>1.830880355651578</v>
+        <v>2.138573257335553</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -832,13 +832,13 @@
         <v>2676</v>
       </c>
       <c r="I19">
-        <v>-1.6713905940354644e-9</v>
+        <v>-3.5131224890899698e-6</v>
       </c>
       <c r="J19">
-        <v>-3.3017992480433187e-6</v>
+        <v>-4.065796363395889e-6</v>
       </c>
       <c r="K19">
-        <v>1.7061801780122623</v>
+        <v>1.7906084221428893</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -867,13 +867,13 @@
         <v>3138</v>
       </c>
       <c r="I20">
-        <v>-5.726356347241152e-10</v>
+        <v>-6.949079963893078e-7</v>
       </c>
       <c r="J20">
-        <v>-1.1463369671928869e-6</v>
+        <v>-1.0771833832459316e-6</v>
       </c>
       <c r="K20">
-        <v>1.4809237898185645</v>
+        <v>1.5425317416384823</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -902,13 +902,13 @@
         <v>3330</v>
       </c>
       <c r="I21">
-        <v>-4.688112214804224e-10</v>
+        <v>-6.99486874284995e-7</v>
       </c>
       <c r="J21">
-        <v>-9.493802338019109e-7</v>
+        <v>-1.0163530109508313e-6</v>
       </c>
       <c r="K21">
-        <v>1.4405358669681665</v>
+        <v>1.5308323325900222</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -937,13 +937,13 @@
         <v>3738</v>
       </c>
       <c r="I22">
-        <v>-4.1403279255267884e-10</v>
+        <v>-8.209368865385035e-7</v>
       </c>
       <c r="J22">
-        <v>-8.536140509836607e-7</v>
+        <v>-9.132440174484374e-7</v>
       </c>
       <c r="K22">
-        <v>1.4186114329117743</v>
+        <v>1.4583749934502785</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -972,13 +972,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-3.9018767439964436e-10</v>
+        <v>-7.453223348750017e-7</v>
       </c>
       <c r="J23">
-        <v>-7.846408376164452e-7</v>
+        <v>-8.055989578580791e-7</v>
       </c>
       <c r="K23">
-        <v>1.3998930027820335</v>
+        <v>1.425711519834341</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-3.4539008298484053e-10</v>
+        <v>-7.337715416014402e-7</v>
       </c>
       <c r="J24">
-        <v>-6.948073510581673e-7</v>
+        <v>-7.496052431892378e-7</v>
       </c>
       <c r="K24">
-        <v>1.372872533562359</v>
+        <v>1.395846212100644</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-3.3792401865104484e-10</v>
+        <v>-6.816908925777774e-7</v>
       </c>
       <c r="J25">
-        <v>-6.803536954811046e-7</v>
+        <v>-7.136617482738427e-7</v>
       </c>
       <c r="K25">
-        <v>1.3693060910337573</v>
+        <v>1.3916625629314257</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1077,13 +1077,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-3.204287557922145e-10</v>
+        <v>-5.965269400368191e-7</v>
       </c>
       <c r="J26">
-        <v>-6.348386253590839e-7</v>
+        <v>-6.427397319456786e-7</v>
       </c>
       <c r="K26">
-        <v>1.3527063114414675</v>
+        <v>1.3762905902830087</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1112,13 +1112,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-3.107626747750734e-10</v>
+        <v>-6.334291678208385e-7</v>
       </c>
       <c r="J27">
-        <v>-6.266860780739141e-7</v>
+        <v>-6.58639820066526e-7</v>
       </c>
       <c r="K27">
-        <v>1.3513107406876987</v>
+        <v>1.371739559375806</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1147,13 +1147,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-2.9577731523261096e-10</v>
+        <v>-6.239212107940752e-7</v>
       </c>
       <c r="J28">
-        <v>-5.961428464812131e-7</v>
+        <v>-6.403911170317289e-7</v>
       </c>
       <c r="K28">
-        <v>1.3400928692800151</v>
+        <v>1.3627438070646956</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1182,13 +1182,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-3.023970375640715e-10</v>
+        <v>-6.633083305564593e-7</v>
       </c>
       <c r="J29">
-        <v>-6.121906822960393e-7</v>
+        <v>-6.683745830562179e-7</v>
       </c>
       <c r="K29">
-        <v>1.3464615561077284</v>
+        <v>1.3670550423585788</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1217,13 +1217,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-2.85677431504904e-10</v>
+        <v>-6.06919139070954e-7</v>
       </c>
       <c r="J30">
-        <v>-5.757422727507396e-7</v>
+        <v>-6.184049739497561e-7</v>
       </c>
       <c r="K30">
-        <v>1.332693441618083</v>
+        <v>1.3530571001362872</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1252,13 +1252,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-2.698672826806508e-10</v>
+        <v>-6.008205952924828e-7</v>
       </c>
       <c r="J31">
-        <v>-5.476906711569192e-7</v>
+        <v>-6.031301385715131e-7</v>
       </c>
       <c r="K31">
-        <v>1.3224092410116965</v>
+        <v>1.343580168692294</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1287,13 +1287,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-2.7240534435783026e-10</v>
+        <v>-5.721789530757297e-7</v>
       </c>
       <c r="J32">
-        <v>-5.508288535506155e-7</v>
+        <v>-5.875809695047058e-7</v>
       </c>
       <c r="K32">
-        <v>1.3235198079416333</v>
+        <v>1.3438434877793184</v>
       </c>
     </row>
   </sheetData>
